--- a/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,172 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>750300</v>
+      </c>
+      <c r="E8" s="3">
         <v>766600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>745400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>550700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>388200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>249500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>157200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>99400</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E9" s="3">
         <v>65100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>29600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>683300</v>
+      </c>
+      <c r="E10" s="3">
         <v>701500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>698700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>521100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>374200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>243500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>154200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>98100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,44 +848,48 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E12" s="3">
         <v>143100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>125900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>61800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>29300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>11500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5700</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,33 +923,36 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E14" s="3">
         <v>15100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -943,35 +962,38 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E15" s="3">
         <v>54200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>34500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>13600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9800</v>
-      </c>
-      <c r="I15" s="3">
-        <v>9100</v>
       </c>
       <c r="J15" s="3">
         <v>9100</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
+      <c r="K15" s="3">
+        <v>9100</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
@@ -979,9 +1001,12 @@
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,80 +1018,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>781300</v>
+      </c>
+      <c r="E17" s="3">
         <v>764800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>732000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>826400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>253400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>175100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>110600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>80600</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-275700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>134800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>74400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>46600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,65 +1113,69 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E20" s="3">
         <v>9300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E21" s="3">
         <v>65200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>48000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-257100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>146100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>84300</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1152,117 +1188,129 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E22" s="3">
         <v>34200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-23200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-303500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>83000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>52300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>39700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>15100</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E24" s="3">
         <v>9600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>10900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6200</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,81 +1344,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-293600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>66000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>43800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8900</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-293600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>66000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>43800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,81 +1578,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-293600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>66000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8900</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,86 +1695,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-293600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>66000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8900</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,29 +1815,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>672300</v>
+      </c>
+      <c r="E41" s="3">
         <v>757200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>941100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>968700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>34600</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,9 +1851,12 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1801,30 +1890,33 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E43" s="3">
         <v>121700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>126400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>97300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>35000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1837,9 +1929,12 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1873,30 +1968,33 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E45" s="3">
         <v>40900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>21300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,30 +2007,33 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>872800</v>
+      </c>
+      <c r="E46" s="3">
         <v>919700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1088800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1086400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>86600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,9 +2046,12 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1981,30 +2085,33 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E48" s="3">
         <v>55700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>49300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>50800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,30 +2124,33 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>567100</v>
+      </c>
+      <c r="E49" s="3">
         <v>602100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>463500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>317800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>262700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>238700</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,9 +2163,12 @@
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,30 +2241,33 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>103000</v>
+      </c>
+      <c r="E52" s="3">
         <v>27200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,30 +2319,33 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1588800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1604600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1607600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1470100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>386800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>314800</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,29 +2395,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E57" s="3">
         <v>17700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2301,14 +2431,17 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7000</v>
+        <v>8800</v>
       </c>
       <c r="E58" s="3">
         <v>7000</v>
@@ -2320,11 +2453,11 @@
         <v>7000</v>
       </c>
       <c r="H58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,30 +2470,33 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77500</v>
+      </c>
+      <c r="E59" s="3">
         <v>51600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>56600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,30 +2509,33 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>122600</v>
+      </c>
+      <c r="E60" s="3">
         <v>76300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>81100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>59600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16600</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,30 +2548,33 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>647700</v>
+      </c>
+      <c r="E61" s="3">
         <v>651800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>655900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>659900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>663900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>716800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2445,30 +2587,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E62" s="3">
         <v>61700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>39000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>39300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>40100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,30 +2743,33 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>826800</v>
+      </c>
+      <c r="E66" s="3">
         <v>789800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>775900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>758800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>737400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>740200</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2729,13 +2896,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>737000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>737000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>737000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,30 +2955,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1457400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1096800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1162900</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,30 +3111,33 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>762000</v>
+      </c>
+      <c r="E76" s="3">
         <v>814800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>831700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>711400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1087600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1162400</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,86 +3189,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-293600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>66000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8900</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,29 +3292,30 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>107700</v>
+      </c>
+      <c r="E83" s="3">
         <v>54200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9800</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3130,9 +3328,12 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,30 +3523,33 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>138300</v>
+      </c>
+      <c r="E89" s="3">
         <v>146800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>178800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>131300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>83300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>45300</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,29 +3582,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3398,9 +3618,12 @@
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,30 +3696,33 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-210500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-178700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-37100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3500</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,30 +3908,33 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-167400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-120200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>905800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-54800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24700</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,9 +3947,12 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3738,30 +3986,33 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-183900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>945500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17100</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3774,7 +4025,10 @@
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -662,7 +662,9 @@
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -699,8 +701,8 @@
       <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
-        <v>43100</v>
+      <c r="J7" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K7" s="2">
         <v>42735</v>
@@ -738,8 +740,8 @@
       <c r="I8" s="3">
         <v>249500</v>
       </c>
-      <c r="J8" s="3">
-        <v>157200</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>99400</v>
@@ -760,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>66900</v>
+        <v>62400</v>
       </c>
       <c r="E9" s="3">
         <v>65100</v>
@@ -777,8 +779,8 @@
       <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
-        <v>3100</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>1200</v>
@@ -799,7 +801,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>683300</v>
+        <v>687800</v>
       </c>
       <c r="E10" s="3">
         <v>701500</v>
@@ -816,8 +818,8 @@
       <c r="I10" s="3">
         <v>243500</v>
       </c>
-      <c r="J10" s="3">
-        <v>154200</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>98100</v>
@@ -855,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>135800</v>
+        <v>126400</v>
       </c>
       <c r="E12" s="3">
         <v>143100</v>
@@ -872,8 +874,8 @@
       <c r="I12" s="3">
         <v>43900</v>
       </c>
-      <c r="J12" s="3">
-        <v>11500</v>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K12" s="3">
         <v>5700</v>
@@ -933,16 +935,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5800</v>
+        <v>80900</v>
       </c>
       <c r="E14" s="3">
-        <v>15100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+        <v>37800</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>1000</v>
+        <v>2100</v>
       </c>
       <c r="H14" s="3">
         <v>4900</v>
@@ -950,8 +952,8 @@
       <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
-        <v>3700</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
@@ -972,7 +974,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>107700</v>
+        <v>61000</v>
       </c>
       <c r="E15" s="3">
         <v>54200</v>
@@ -990,7 +992,7 @@
         <v>9800</v>
       </c>
       <c r="J15" s="3">
-        <v>9100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>9100</v>
@@ -1025,25 +1027,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>781300</v>
+        <v>700300</v>
       </c>
       <c r="E17" s="3">
-        <v>764800</v>
+        <v>727000</v>
       </c>
       <c r="F17" s="3">
         <v>732000</v>
       </c>
       <c r="G17" s="3">
-        <v>826400</v>
+        <v>824400</v>
       </c>
       <c r="H17" s="3">
-        <v>253400</v>
+        <v>248500</v>
       </c>
       <c r="I17" s="3">
-        <v>175100</v>
-      </c>
-      <c r="J17" s="3">
-        <v>110600</v>
+        <v>172300</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>80600</v>
@@ -1064,25 +1066,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-31000</v>
+        <v>49900</v>
       </c>
       <c r="E18" s="3">
-        <v>1700</v>
+        <v>39500</v>
       </c>
       <c r="F18" s="3">
         <v>13400</v>
       </c>
       <c r="G18" s="3">
-        <v>-275700</v>
+        <v>-273700</v>
       </c>
       <c r="H18" s="3">
-        <v>134800</v>
+        <v>139700</v>
       </c>
       <c r="I18" s="3">
-        <v>74400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>46600</v>
+        <v>77300</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>18800</v>
@@ -1119,26 +1121,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>32200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>9300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>100</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-2300</v>
+        <v>3000</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>-100</v>
@@ -1159,25 +1161,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>108800</v>
+        <v>110900</v>
       </c>
       <c r="E21" s="3">
-        <v>65200</v>
+        <v>93700</v>
       </c>
       <c r="F21" s="3">
-        <v>48000</v>
+        <v>47900</v>
       </c>
       <c r="G21" s="3">
-        <v>-257100</v>
+        <v>-255200</v>
       </c>
       <c r="H21" s="3">
-        <v>146100</v>
+        <v>150300</v>
       </c>
       <c r="I21" s="3">
-        <v>84300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>87100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1215,8 +1217,8 @@
       <c r="I22" s="3">
         <v>22200</v>
       </c>
-      <c r="J22" s="3">
-        <v>7000</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>3500</v>
@@ -1254,8 +1256,8 @@
       <c r="I23" s="3">
         <v>52300</v>
       </c>
-      <c r="J23" s="3">
-        <v>39700</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>15100</v>
@@ -1293,8 +1295,8 @@
       <c r="I24" s="3">
         <v>8600</v>
       </c>
-      <c r="J24" s="3">
-        <v>10900</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>6200</v>
@@ -1371,8 +1373,8 @@
       <c r="I26" s="3">
         <v>43800</v>
       </c>
-      <c r="J26" s="3">
-        <v>28800</v>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>8900</v>
@@ -1405,13 +1407,13 @@
         <v>-293600</v>
       </c>
       <c r="H27" s="3">
-        <v>66000</v>
+        <v>42400</v>
       </c>
       <c r="I27" s="3">
-        <v>43800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>28800</v>
+        <v>13800</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>8900</v>
@@ -1587,26 +1589,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-32200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-9300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-100</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>2300</v>
+        <v>-3000</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>100</v>
@@ -1644,8 +1646,8 @@
       <c r="I33" s="3">
         <v>43800</v>
       </c>
-      <c r="J33" s="3">
-        <v>28800</v>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>8900</v>
@@ -1722,8 +1724,8 @@
       <c r="I35" s="3">
         <v>43800</v>
       </c>
-      <c r="J35" s="3">
-        <v>28800</v>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>8900</v>
@@ -1766,8 +1768,8 @@
       <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
-        <v>43100</v>
+      <c r="J38" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K38" s="2">
         <v>42735</v>
@@ -1900,7 +1902,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>147100</v>
+        <v>175500</v>
       </c>
       <c r="E43" s="3">
         <v>121700</v>
@@ -1912,7 +1914,7 @@
         <v>97300</v>
       </c>
       <c r="H43" s="3">
-        <v>48100</v>
+        <v>55500</v>
       </c>
       <c r="I43" s="3">
         <v>35000</v>
@@ -1938,26 +1940,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1977,23 +1979,23 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>53300</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E45" s="3">
-        <v>40900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>21300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>20400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>12400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>3400</v>
+        <v>5800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2056,25 +2058,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>4000</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2251,22 +2253,22 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>103000</v>
+        <v>22800</v>
       </c>
       <c r="E52" s="3">
-        <v>27200</v>
+        <v>8200</v>
       </c>
       <c r="F52" s="3">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="G52" s="3">
-        <v>15100</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>3400</v>
+        <v>1200</v>
       </c>
       <c r="I52" s="3">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2441,19 +2443,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8800</v>
+        <v>15000</v>
       </c>
       <c r="E58" s="3">
-        <v>7000</v>
+        <v>11100</v>
       </c>
       <c r="F58" s="3">
-        <v>7000</v>
+        <v>12900</v>
       </c>
       <c r="G58" s="3">
-        <v>7000</v>
+        <v>11600</v>
       </c>
       <c r="H58" s="3">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="I58" s="3">
         <v>5400</v>
@@ -2480,22 +2482,22 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>77500</v>
+        <v>7100</v>
       </c>
       <c r="E59" s="3">
-        <v>51600</v>
+        <v>7900</v>
       </c>
       <c r="F59" s="3">
-        <v>56600</v>
+        <v>6900</v>
       </c>
       <c r="G59" s="3">
-        <v>42200</v>
+        <v>6900</v>
       </c>
       <c r="H59" s="3">
-        <v>18500</v>
+        <v>4800</v>
       </c>
       <c r="I59" s="3">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2558,19 +2560,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>647700</v>
+        <v>696100</v>
       </c>
       <c r="E61" s="3">
-        <v>651800</v>
+        <v>705900</v>
       </c>
       <c r="F61" s="3">
-        <v>655900</v>
+        <v>689500</v>
       </c>
       <c r="G61" s="3">
-        <v>659900</v>
+        <v>693400</v>
       </c>
       <c r="H61" s="3">
-        <v>663900</v>
+        <v>701000</v>
       </c>
       <c r="I61" s="3">
         <v>716800</v>
@@ -2597,22 +2599,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>56600</v>
+        <v>8200</v>
       </c>
       <c r="E62" s="3">
-        <v>61700</v>
+        <v>7600</v>
       </c>
       <c r="F62" s="3">
-        <v>39000</v>
+        <v>5400</v>
       </c>
       <c r="G62" s="3">
-        <v>39300</v>
+        <v>5800</v>
       </c>
       <c r="H62" s="3">
-        <v>40100</v>
+        <v>3000</v>
       </c>
       <c r="I62" s="3">
-        <v>6800</v>
+        <v>3300</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -3221,8 +3223,8 @@
       <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
-        <v>43100</v>
+      <c r="J80" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="K80" s="2">
         <v>42735</v>
@@ -3260,8 +3262,8 @@
       <c r="I81" s="3">
         <v>43800</v>
       </c>
-      <c r="J81" s="3">
-        <v>28800</v>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>8900</v>
@@ -3299,22 +3301,22 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>107700</v>
+        <v>4800</v>
       </c>
       <c r="E83" s="3">
-        <v>54200</v>
+        <v>4600</v>
       </c>
       <c r="F83" s="3">
-        <v>34500</v>
+        <v>4000</v>
       </c>
       <c r="G83" s="3">
-        <v>18400</v>
+        <v>1300</v>
       </c>
       <c r="H83" s="3">
-        <v>13600</v>
+        <v>700</v>
       </c>
       <c r="I83" s="3">
-        <v>9800</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -3956,26 +3958,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4013,8 +4015,8 @@
       <c r="I102" s="3">
         <v>17100</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,186 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2">
+      <c r="K7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>792300</v>
+      </c>
+      <c r="E8" s="3">
         <v>750300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>766600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>745400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>550700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>388200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>249500</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>99400</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E9" s="3">
         <v>62400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>65100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>29600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>14000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>744100</v>
+      </c>
+      <c r="E10" s="3">
         <v>687800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>701500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>698700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>521100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>374200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>243500</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="3">
         <v>98100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -851,47 +863,51 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E12" s="3">
         <v>126400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>143100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>125900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>61800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>29300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>43900</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>5700</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -928,33 +944,36 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>80900</v>
+        <v>22400</v>
       </c>
       <c r="E14" s="3">
-        <v>37800</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+        <v>81000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>18100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>2100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -967,48 +986,54 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E15" s="3">
         <v>61000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>34500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>18400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>13600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9800</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>9100</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1021,86 +1046,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>700300</v>
+        <v>706100</v>
       </c>
       <c r="E17" s="3">
-        <v>727000</v>
+        <v>700200</v>
       </c>
       <c r="F17" s="3">
+        <v>746800</v>
+      </c>
+      <c r="G17" s="3">
         <v>732000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>824400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>248500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>172300</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L17" s="3">
         <v>80600</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>49900</v>
+        <v>86200</v>
       </c>
       <c r="E18" s="3">
-        <v>39500</v>
+        <v>50000</v>
       </c>
       <c r="F18" s="3">
+        <v>19800</v>
+      </c>
+      <c r="G18" s="3">
         <v>13400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-273700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>139700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>77300</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3">
         <v>18800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1116,13 +1148,14 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>2700</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1130,59 +1163,62 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>3000</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>110900</v>
+        <v>153100</v>
       </c>
       <c r="E21" s="3">
-        <v>93700</v>
+        <v>111000</v>
       </c>
       <c r="F21" s="3">
+        <v>74000</v>
+      </c>
+      <c r="G21" s="3">
         <v>47900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-255200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>150300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>87100</v>
       </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
@@ -1193,126 +1229,138 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E22" s="3">
         <v>56700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>23600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>49600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22200</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>3500</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-303500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>83000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>52300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L23" s="3">
         <v>15100</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-46700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-9800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8600</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1349,87 +1397,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-8900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-293600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>66000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43800</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="3">
         <v>8900</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-8900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-293600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>42400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13800</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L27" s="3">
         <v>8900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1466,9 +1523,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1505,9 +1565,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1544,9 +1607,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1583,14 +1649,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-2700</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -1598,72 +1667,78 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-3000</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-8900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-293600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>66000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>43800</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="3">
         <v>8900</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1700,92 +1775,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-8900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-293600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>66000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>43800</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L35" s="3">
         <v>8900</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2">
+      <c r="K38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,8 +1885,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1818,32 +1903,33 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>448300</v>
+      </c>
+      <c r="E41" s="3">
         <v>672300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>757200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>941100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>968700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>34600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1856,9 +1942,12 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1895,33 +1984,36 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E43" s="3">
         <v>175500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>121700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>126400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>97300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>55500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>35000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,9 +2026,12 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1961,8 +2056,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -1973,21 +2068,24 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>5800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2012,33 +2110,36 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>659300</v>
+      </c>
+      <c r="E46" s="3">
         <v>872800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>919700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1088800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1086400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>86600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>73100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2051,9 +2152,12 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2061,14 +2165,14 @@
         <v>15000</v>
       </c>
       <c r="E47" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F47" s="3">
         <v>19000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2078,8 +2182,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2090,33 +2194,36 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E48" s="3">
         <v>45900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>49300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>50800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2129,33 +2236,36 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>587700</v>
+      </c>
+      <c r="E49" s="3">
         <v>567100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>602100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>463500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>317800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>262700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>238700</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2168,9 +2278,12 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2207,9 +2320,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2246,32 +2362,35 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E52" s="3">
         <v>22800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>2000</v>
       </c>
       <c r="G52" s="3">
         <v>2000</v>
       </c>
       <c r="H52" s="3">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="I52" s="3">
         <v>1200</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>1200</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2285,9 +2404,12 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2324,33 +2446,36 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1388100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1588800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1604600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1607600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1470100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>386800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>314800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,9 +2488,12 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2381,8 +2509,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2398,32 +2527,33 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E57" s="3">
         <v>36300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7200</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,33 +2566,36 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E58" s="3">
         <v>15000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5400</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,33 +2608,36 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7900</v>
-      </c>
-      <c r="F59" s="3">
-        <v>6900</v>
       </c>
       <c r="G59" s="3">
         <v>6900</v>
       </c>
       <c r="H59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="I59" s="3">
         <v>4800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2514,33 +2650,36 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>123900</v>
+      </c>
+      <c r="E60" s="3">
         <v>122600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>76300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>81100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>59600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>16600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2553,33 +2692,36 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>532800</v>
+      </c>
+      <c r="E61" s="3">
         <v>696100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>705900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>689500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>693400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>701000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>716800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2592,33 +2734,36 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E62" s="3">
         <v>8200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>7600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,9 +2776,12 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2670,9 +2818,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2709,9 +2860,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2748,33 +2902,36 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>663400</v>
+      </c>
+      <c r="E66" s="3">
         <v>826800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>789800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>775900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>758800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>737400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>740200</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2787,9 +2944,12 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2805,8 +2965,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2843,9 +3004,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2882,9 +3046,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2901,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>737000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
         <v>737000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>737000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2921,9 +3088,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2960,33 +3130,36 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1441000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1096800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1162900</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2999,9 +3172,12 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3038,9 +3214,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3077,9 +3256,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3116,33 +3298,36 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>724700</v>
+      </c>
+      <c r="E76" s="3">
         <v>762000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>814800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>831700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>711400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1087600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1162400</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3155,9 +3340,12 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3194,92 +3382,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2">
+      <c r="K80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-8900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-293600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>66000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>43800</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L81" s="3">
         <v>8900</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3295,32 +3492,33 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E83" s="3">
         <v>4800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3333,9 +3531,12 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3372,9 +3573,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3411,9 +3615,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3450,9 +3657,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3489,9 +3699,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3528,33 +3741,36 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>183900</v>
+      </c>
+      <c r="E89" s="3">
         <v>138300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>146800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>178800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>131300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>45300</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3567,9 +3783,12 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3585,32 +3804,33 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,9 +3843,12 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3662,9 +3885,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3701,33 +3927,36 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-210500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-178700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-91600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-37100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3740,9 +3969,12 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3758,8 +3990,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3796,9 +4029,12 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3835,9 +4071,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3874,9 +4113,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3913,33 +4155,36 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-337500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-167400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-120200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>905800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-54800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24700</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3952,9 +4197,12 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3979,8 +4227,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3991,35 +4239,38 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-224000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-84900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-183900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-30500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>945500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>17100</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
@@ -4030,7 +4281,10 @@
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GDRX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="92">
   <si>
     <t>GDRX</t>
   </si>
@@ -656,198 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>796900</v>
+      </c>
+      <c r="E8" s="3">
         <v>792300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>750300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>766600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>745400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>550700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>388200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>249500</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>99400</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>57600</v>
+      </c>
+      <c r="E9" s="3">
         <v>48200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>62400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>65100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>46700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>29600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>739300</v>
+      </c>
+      <c r="E10" s="3">
         <v>744100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>687800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>701500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>698700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>521100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>374200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>243500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>98100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,50 +876,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E12" s="3">
         <v>123700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>126400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>143100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>125900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>61800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>29300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>43900</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>5700</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,36 +963,39 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E14" s="3">
         <v>22400</v>
       </c>
-      <c r="E14" s="3">
-        <v>81000</v>
-      </c>
       <c r="F14" s="3">
+        <v>76500</v>
+      </c>
+      <c r="G14" s="3">
         <v>18100</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>2100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -989,51 +1008,57 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>85200</v>
+      </c>
+      <c r="E15" s="3">
         <v>69500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>61000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>54200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>34500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>18400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9800</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>9100</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1047,92 +1072,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>690700</v>
+      </c>
+      <c r="E17" s="3">
         <v>706100</v>
       </c>
-      <c r="E17" s="3">
-        <v>700200</v>
-      </c>
       <c r="F17" s="3">
+        <v>700800</v>
+      </c>
+      <c r="G17" s="3">
         <v>746800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>732000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>824400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>248500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>172300</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>80600</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>106200</v>
+      </c>
+      <c r="E18" s="3">
         <v>86200</v>
       </c>
-      <c r="E18" s="3">
-        <v>50000</v>
-      </c>
       <c r="F18" s="3">
+        <v>49500</v>
+      </c>
+      <c r="G18" s="3">
         <v>19800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-273700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>139700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>77300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>18800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1149,79 +1181,83 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2700</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
+      <c r="F20" s="3">
+        <v>4000</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>3000</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>192100</v>
+      </c>
+      <c r="E21" s="3">
         <v>153100</v>
       </c>
-      <c r="E21" s="3">
-        <v>111000</v>
-      </c>
       <c r="F21" s="3">
+        <v>106500</v>
+      </c>
+      <c r="G21" s="3">
         <v>74000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>47900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-255200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>150300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>87100</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
+      <c r="L21" s="3">
+        <v>0</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
@@ -1232,135 +1268,147 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E22" s="3">
         <v>52900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>23600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>49600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22200</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
         <v>3500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E23" s="3">
         <v>31500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-303500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>83000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>52300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>15100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E24" s="3">
         <v>15100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-46700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>15100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>16900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8600</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>6200</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1400,93 +1448,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E26" s="3">
         <v>16400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-293600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>66000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43800</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>8900</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E27" s="3">
         <v>16400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-293600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>42400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>8900</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1526,9 +1583,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1568,9 +1628,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1610,9 +1673,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1652,93 +1718,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2700</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
+      <c r="F32" s="3">
+        <v>-4000</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3000</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E33" s="3">
         <v>16400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-293600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>66000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43800</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>8900</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1778,98 +1853,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E35" s="3">
         <v>16400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-293600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>66000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43800</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>8900</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1886,8 +1970,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1904,35 +1989,36 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>261800</v>
+      </c>
+      <c r="E41" s="3">
         <v>448300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>672300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>757200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>941100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>968700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>34600</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,9 +2031,12 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1987,36 +2076,39 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>183800</v>
+        <v>254900</v>
       </c>
       <c r="E43" s="3">
+        <v>160800</v>
+      </c>
+      <c r="F43" s="3">
         <v>175500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>121700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>126400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>97300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>55500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>35000</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2029,9 +2121,12 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2059,8 +2154,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2071,24 +2166,27 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>22900</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>5800</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2113,36 +2211,39 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>643100</v>
+      </c>
+      <c r="E46" s="3">
         <v>659300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>872800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>919700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1088800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1086400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>86600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>73100</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2155,9 +2256,12 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2168,14 +2272,14 @@
         <v>15000</v>
       </c>
       <c r="F47" s="3">
+        <v>15000</v>
+      </c>
+      <c r="G47" s="3">
         <v>19000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,8 +2289,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2197,36 +2301,39 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E48" s="3">
         <v>40500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>55700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>50800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1000</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,36 +2346,39 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>633700</v>
+      </c>
+      <c r="E49" s="3">
         <v>587700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>567100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>602100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>463500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>317800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>262700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>238700</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,9 +2391,12 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2323,9 +2436,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2365,35 +2481,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>2000</v>
       </c>
       <c r="H52" s="3">
         <v>2000</v>
       </c>
       <c r="I52" s="3">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="J52" s="3">
         <v>1200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>1200</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2407,9 +2526,12 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2449,36 +2571,39 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1404100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1388100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1588800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1604600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1607600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1470100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>386800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>314800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2491,9 +2616,12 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2510,8 +2638,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2528,35 +2657,36 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E57" s="3">
         <v>14100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2569,36 +2699,39 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E58" s="3">
         <v>10600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5400</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,36 +2744,39 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136800</v>
+      </c>
+      <c r="E59" s="3">
         <v>23300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7900</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6900</v>
       </c>
       <c r="H59" s="3">
         <v>6900</v>
       </c>
       <c r="I59" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J59" s="3">
         <v>4800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2653,36 +2789,39 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>246000</v>
+      </c>
+      <c r="E60" s="3">
         <v>123900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>122600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>76300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>81100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>59600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,36 +2834,39 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>533100</v>
+      </c>
+      <c r="E61" s="3">
         <v>532800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>696100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>705900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>689500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>693400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>701000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>716800</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2737,36 +2879,39 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E62" s="3">
         <v>6800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2779,9 +2924,12 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2821,9 +2969,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2863,9 +3014,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2905,36 +3059,39 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>787800</v>
+      </c>
+      <c r="E66" s="3">
         <v>663400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>826800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>789800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>775900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>758800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>737400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>740200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2947,9 +3104,12 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2966,8 +3126,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3007,9 +3168,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3049,9 +3213,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3071,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>737000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>737000</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>737000</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3091,9 +3258,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3133,36 +3303,39 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1410600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1441000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1457400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1448500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1415700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1390500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1096800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1162900</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,9 +3348,12 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3217,9 +3393,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3259,9 +3438,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3301,36 +3483,39 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>616300</v>
+      </c>
+      <c r="E76" s="3">
         <v>724700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>762000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>814800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>831700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>711400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1087600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1162400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3343,9 +3528,12 @@
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3385,98 +3573,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E81" s="3">
         <v>16400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-293600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>66000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43800</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>8900</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3493,35 +3690,36 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E83" s="3">
         <v>4500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3534,9 +3732,12 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3576,9 +3777,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3618,9 +3822,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3660,9 +3867,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3702,9 +3912,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3744,36 +3957,39 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>167900</v>
+      </c>
+      <c r="E89" s="3">
         <v>183900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>138300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>146800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>178800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>131300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>45300</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3786,9 +4002,12 @@
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3805,35 +4024,36 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-20600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,9 +4066,12 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3888,9 +4111,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3930,36 +4156,39 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-120000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-70300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-55800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-210500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-178700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-91600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-37100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3972,9 +4201,12 @@
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3991,8 +4223,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4032,9 +4265,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4074,9 +4310,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4116,9 +4355,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4158,36 +4400,39 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-234500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-337500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-167400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-120200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-30500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>905800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-54800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4200,9 +4445,12 @@
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4230,8 +4478,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4242,38 +4490,41 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-186500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-224000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-84900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-183900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-30500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>945500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17100</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4284,7 +4535,10 @@
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
